--- a/data/FlowSedimentData.xlsx
+++ b/data/FlowSedimentData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12220" activeTab="1"/>
+    <workbookView windowHeight="18700"/>
   </bookViews>
   <sheets>
     <sheet name="Unsteady Flow Data" sheetId="1" r:id="rId1"/>
@@ -1639,9 +1639,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10.5576923076923" style="3" customWidth="1"/>
-    <col min="2" max="2" width="12.7788461538462" style="3" customWidth="1"/>
-    <col min="3" max="3" width="23.7788461538462" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.7788461538462" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.7788461538462" style="3" customWidth="1"/>
+    <col min="3" max="3" width="25.1538461538462" style="3" customWidth="1"/>
+    <col min="4" max="4" width="16.6634615384615" style="3" customWidth="1"/>
     <col min="5" max="5" width="23.7788461538462" style="3" customWidth="1"/>
     <col min="6" max="16384" width="9" style="3"/>
   </cols>
